--- a/backtest_runs/20260410_193731/by_symbol/PPP/PPP.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/PPP/PPP.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>100000</v>
@@ -679,7 +679,7 @@
         <v>-4099.110000000001</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>95900.89</v>
@@ -817,7 +817,7 @@
         <v>-471.8400000000039</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>101179.6</v>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>101179.6</v>
@@ -955,7 +955,7 @@
         <v>-884.7000000000056</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>101238.58</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>101238.58</v>
@@ -1231,7 +1231,7 @@
         <v>-4610.269999999998</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>99184.11</v>
@@ -1323,7 +1323,7 @@
         <v>-49.15000000001118</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>99134.95999999999</v>
@@ -1461,7 +1461,7 @@
         <v>-216.2599999999989</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>101464.67</v>
@@ -1507,7 +1507,7 @@
         <v>-324.3899999999983</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>101140.28</v>
@@ -1553,7 +1553,7 @@
         <v>-619.2899999999955</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>100520.99</v>
@@ -1645,7 +1645,7 @@
         <v>-4285.879999999999</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>106143.75</v>
